--- a/excelDataSource/20260609_涨停复盘_verified.xlsx
+++ b/excelDataSource/20260609_涨停复盘_verified.xlsx
@@ -5170,7 +5170,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>板块标题全部识别成功，各板块声明数量与提取股票数一致，自动校验通过。</t>
+          <t>03/04均识别成功，板块标题与声明数量校验通过。</t>
         </is>
       </c>
     </row>

--- a/excelDataSource/20260609_涨停复盘_verified.xlsx
+++ b/excelDataSource/20260609_涨停复盘_verified.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24220" windowHeight="9880" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03提取" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04提取" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03提取" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="04提取" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -4870,17 +4870,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>600719</t>
+          <t>000029</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>大连热电</t>
+          <t>深深房A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>9:49</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>热电联产</t>
+          <t>地产</t>
         </is>
       </c>
     </row>
@@ -4902,27 +4902,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>000037</t>
+          <t>000608</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>深南电A</t>
+          <t>阳光股份</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1/3天2板</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>供电供热</t>
+          <t>地产</t>
         </is>
       </c>
     </row>
@@ -4934,17 +4934,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>600396</t>
+          <t>603303</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>华电辽能</t>
+          <t>得邦照明</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>绿色电力</t>
+          <t>LED照明</t>
         </is>
       </c>
     </row>
@@ -4966,17 +4966,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>000048</t>
+          <t>600719</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>京基智农</t>
+          <t>大连热电</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>猪价反弹</t>
+          <t>热电联产</t>
         </is>
       </c>
     </row>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>001215</t>
+          <t>600719</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>千味央厨</t>
+          <t>大连热电</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>与伊利合作</t>
+          <t>热电联产</t>
         </is>
       </c>
     </row>
@@ -5030,27 +5030,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>603020</t>
+          <t>000037</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>爱普股份</t>
+          <t>深南电A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1/3天2板</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>电子烟+收购进展</t>
+          <t>供电供热</t>
         </is>
       </c>
     </row>
@@ -5062,27 +5062,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>001696</t>
+          <t>000037</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>宗申动力</t>
+          <t>深南电A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>9:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>供电供热</t>
         </is>
       </c>
     </row>
@@ -5094,27 +5094,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>002051</t>
+          <t>600396</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>中工国际</t>
+          <t>华电辽能</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>9:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1/4天2板</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>基建</t>
+          <t>绿色电力</t>
         </is>
       </c>
     </row>
@@ -5126,17 +5126,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>603335</t>
+          <t>600396</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>迪生力</t>
+          <t>华电辽能</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>绿色电力</t>
         </is>
       </c>
     </row>
